--- a/02table/TableS4_Non-additive_gene.xlsx
+++ b/02table/TableS4_Non-additive_gene.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11113"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A28F3D57-14DE-274C-9437-B948D97D9390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE51507-EBB4-BE4E-935A-EC8F2F823FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="75140" yWindow="-500" windowWidth="30240" windowHeight="17260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19438,7 +19438,7 @@
     </r>
   </si>
   <si>
-    <t>Table S4 Non-additive genes identified by expression data.</t>
+    <t>Table S4. Non-additive genes identified by expression data.</t>
   </si>
 </sst>
 </file>
